--- a/data/attendance/ECOLE_كحال_علوم_رياضي.xlsx
+++ b/data/attendance/ECOLE_كحال_علوم_رياضي.xlsx
@@ -20,63 +20,105 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:73446656-974e-4032-8262-fa332ae760b6</t>
+          <t>student_id:b5434f48-2bed-43a0-ada7-62bd10b64a5e</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:5ca01918-1146-4301-9482-0fd8f6f2b9e1</t>
+          <t>student_id:73446656-974e-4032-8262-fa332ae760b6</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:48a125fe-bb69-4b34-8dd8-b357f3776ad2</t>
+          <t>student_id:5ca01918-1146-4301-9482-0fd8f6f2b9e1</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:acacb8c6-03d8-481e-b6cc-da81abc2eddb</t>
+          <t>student_id:48a125fe-bb69-4b34-8dd8-b357f3776ad2</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:4d5d15c8-b6af-497d-8dc9-cd3ac6a818a0</t>
+          <t>student_id:acacb8c6-03d8-481e-b6cc-da81abc2eddb</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:7f304429-1bb8-4a12-b67b-a06b8388ceca</t>
+          <t>student_id:4d5d15c8-b6af-497d-8dc9-cd3ac6a818a0</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:bd1af0ef-db31-4469-9812-a9ebea743880</t>
+          <t>student_id:b2aa80de-d2f9-47f9-9e3d-e8aaabe829e7</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <t>student_id:963b164f-da65-41e6-b5e8-e9dec2515bf9</t>
+          <t>student_id:7f304429-1bb8-4a12-b67b-a06b8388ceca</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <t>student_id:a147d140-b436-4bd9-8cf8-dda95f58321d</t>
+          <t>student_id:a9f2b729-1881-4aa9-8b7f-c010c77d6ff9</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <t>student_id:bd1af0ef-db31-4469-9812-a9ebea743880</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <t>student_id:f9665799-bcdd-42cb-9ee2-2c0b46fad4a7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <t>student_id:963b164f-da65-41e6-b5e8-e9dec2515bf9</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <t>student_id:c2395d0c-0ddf-48e0-9093-a838b6054764</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <t>student_id:634f91a0-f7b3-4981-be1e-e3cc521b1464</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
+          <t>student_id:ba54c276-ecef-45ad-ab87-1e1766ed57b6</t>
         </r>
       </text>
     </comment>
@@ -85,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
   <si>
     <t>كحال علوم رياضي  |  ECOLE  |  BAC  |  كحال لمياء</t>
   </si>
@@ -99,6 +141,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -108,9 +153,15 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>غربي جمانة</t>
+  </si>
+  <si>
     <t>ربيعي عبد العظيم</t>
   </si>
   <si>
@@ -126,16 +177,31 @@
     <t>ليتيم مليسا</t>
   </si>
   <si>
+    <t>نحال لينا</t>
+  </si>
+  <si>
     <t>بعاج أسماء</t>
   </si>
   <si>
+    <t>شبايكي شهد</t>
+  </si>
+  <si>
     <t>قاولي نهال</t>
   </si>
   <si>
+    <t>عثماني كريم</t>
+  </si>
+  <si>
     <t>مجدوب الاء تسنيم</t>
   </si>
   <si>
-    <t>شبابكي شهد</t>
+    <t>اقيس لجين</t>
+  </si>
+  <si>
+    <t>فنيخ شهد رشا</t>
+  </si>
+  <si>
+    <t>عبد المؤمن دانية اسراء</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -165,7 +231,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -655,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -681,7 +750,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -691,10 +760,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -736,54 +808,54 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -824,10 +896,10 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -868,10 +940,10 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -912,10 +984,10 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -956,10 +1028,10 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -1000,10 +1072,10 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1044,10 +1116,10 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1088,10 +1160,10 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>611</v>
+        <v>149</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1132,10 +1204,10 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>612</v>
+        <v>161</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1171,6 +1243,270 @@
         <v>0</v>
       </c>
       <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>164</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>166</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>611</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>829</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>831</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>832</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1190,7 +1526,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1198,77 +1534,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
